--- a/data/nzd0339/nzd0339.xlsx
+++ b/data/nzd0339/nzd0339.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I494"/>
+  <dimension ref="A1:I495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16736,6 +16736,39 @@
         <v>337.2</v>
       </c>
       <c r="I494" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>379.67</v>
+      </c>
+      <c r="C495" t="n">
+        <v>377.65</v>
+      </c>
+      <c r="D495" t="n">
+        <v>370.22</v>
+      </c>
+      <c r="E495" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="F495" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="G495" t="n">
+        <v>340.45</v>
+      </c>
+      <c r="H495" t="n">
+        <v>336.39</v>
+      </c>
+      <c r="I495" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16752,7 +16785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B516"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21915,6 +21948,16 @@
       </c>
       <c r="B516" t="n">
         <v>-0.98</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -22083,28 +22126,28 @@
         <v>0.188</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06613731935698185</v>
+        <v>-0.06402882737831996</v>
       </c>
       <c r="J2" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K2" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003734125763599661</v>
+        <v>0.00351042045489558</v>
       </c>
       <c r="M2" t="n">
-        <v>6.994625760562655</v>
+        <v>6.993994344069572</v>
       </c>
       <c r="N2" t="n">
-        <v>73.53519976853219</v>
+        <v>73.46003681087009</v>
       </c>
       <c r="O2" t="n">
-        <v>8.575266746202837</v>
+        <v>8.570883082324137</v>
       </c>
       <c r="P2" t="n">
-        <v>375.3628701783153</v>
+        <v>375.3424260192655</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22161,28 +22204,28 @@
         <v>0.1905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1078183204536748</v>
+        <v>0.108683450917608</v>
       </c>
       <c r="J3" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K3" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007540447399182137</v>
+        <v>0.007688975824047262</v>
       </c>
       <c r="M3" t="n">
-        <v>7.513091344832421</v>
+        <v>7.503947942278302</v>
       </c>
       <c r="N3" t="n">
-        <v>96.40878558855852</v>
+        <v>96.22603261830092</v>
       </c>
       <c r="O3" t="n">
-        <v>9.818797563274156</v>
+        <v>9.80948686824652</v>
       </c>
       <c r="P3" t="n">
-        <v>372.3191901905991</v>
+        <v>372.3108017950147</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22239,28 +22282,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09551611919398545</v>
+        <v>0.0937544571427934</v>
       </c>
       <c r="J4" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K4" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007799488977419333</v>
+        <v>0.007539716178711187</v>
       </c>
       <c r="M4" t="n">
-        <v>6.642188342139074</v>
+        <v>6.636674191171728</v>
       </c>
       <c r="N4" t="n">
-        <v>73.13115315671948</v>
+        <v>73.03455803620355</v>
       </c>
       <c r="O4" t="n">
-        <v>8.551675459038391</v>
+        <v>8.546025862130511</v>
       </c>
       <c r="P4" t="n">
-        <v>372.759002644879</v>
+        <v>372.7760839046283</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22317,28 +22360,28 @@
         <v>0.1532</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09195576708098524</v>
+        <v>0.09001812048112795</v>
       </c>
       <c r="J5" t="n">
+        <v>494</v>
+      </c>
+      <c r="K5" t="n">
         <v>493</v>
       </c>
-      <c r="K5" t="n">
-        <v>492</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.006036254080153403</v>
+        <v>0.005803780959252713</v>
       </c>
       <c r="M5" t="n">
-        <v>7.193047949122694</v>
+        <v>7.186371400777753</v>
       </c>
       <c r="N5" t="n">
-        <v>87.84273489129208</v>
+        <v>87.72693186275116</v>
       </c>
       <c r="O5" t="n">
-        <v>9.372445512847332</v>
+        <v>9.366265630588915</v>
       </c>
       <c r="P5" t="n">
-        <v>366.5039848362679</v>
+        <v>366.5227680225944</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22395,28 +22438,28 @@
         <v>0.1625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06809698469475145</v>
+        <v>0.06510961461743044</v>
       </c>
       <c r="J6" t="n">
+        <v>494</v>
+      </c>
+      <c r="K6" t="n">
         <v>493</v>
       </c>
-      <c r="K6" t="n">
-        <v>492</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.003121868902480229</v>
+        <v>0.002861023980838984</v>
       </c>
       <c r="M6" t="n">
-        <v>8.0436645099616</v>
+        <v>8.04121544824145</v>
       </c>
       <c r="N6" t="n">
-        <v>93.40868483806614</v>
+        <v>93.36747260441734</v>
       </c>
       <c r="O6" t="n">
-        <v>9.664816854864149</v>
+        <v>9.66268454439124</v>
       </c>
       <c r="P6" t="n">
-        <v>357.2864919634242</v>
+        <v>357.315453400665</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22473,28 +22516,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009882331758350051</v>
+        <v>0.006735430391957924</v>
       </c>
       <c r="J7" t="n">
+        <v>494</v>
+      </c>
+      <c r="K7" t="n">
         <v>493</v>
       </c>
-      <c r="K7" t="n">
-        <v>492</v>
-      </c>
       <c r="L7" t="n">
-        <v>7.83358608398288e-05</v>
+        <v>3.645273140640004e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>6.977245915202371</v>
+        <v>6.979168025175383</v>
       </c>
       <c r="N7" t="n">
-        <v>78.6372473254179</v>
+        <v>78.64225472822127</v>
       </c>
       <c r="O7" t="n">
-        <v>8.867764505523244</v>
+        <v>8.868046838409306</v>
       </c>
       <c r="P7" t="n">
-        <v>349.2202187886291</v>
+        <v>349.2507268221391</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22551,28 +22594,28 @@
         <v>0.1377</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05180774236420286</v>
+        <v>-0.05466097896412758</v>
       </c>
       <c r="J8" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K8" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002974256007656439</v>
+        <v>0.003314451496820192</v>
       </c>
       <c r="M8" t="n">
-        <v>5.90209683117715</v>
+        <v>5.906499737262004</v>
       </c>
       <c r="N8" t="n">
-        <v>56.69348388339986</v>
+        <v>56.71366641162147</v>
       </c>
       <c r="O8" t="n">
-        <v>7.529507545875751</v>
+        <v>7.530847655584427</v>
       </c>
       <c r="P8" t="n">
-        <v>345.9474921245234</v>
+        <v>345.9751574054189</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22610,7 +22653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I494"/>
+  <dimension ref="A1:I495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45819,6 +45862,53 @@
         </is>
       </c>
     </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>-41.07742620880047,172.10303145361334</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>-41.07675215713583,172.10294358736328</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-41.07607237447223,172.10291967142024</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-41.07539319865339,172.10288889765937</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>-41.07470765694181,172.10292916406598</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-41.07402507098199,172.1029363299998</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-41.07334882670696,172.1028725713529</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0339/nzd0339.xlsx
+++ b/data/nzd0339/nzd0339.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I495"/>
+  <dimension ref="A1:I498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16769,6 +16769,105 @@
         <v>336.39</v>
       </c>
       <c r="I495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>371.52</v>
+      </c>
+      <c r="C496" t="n">
+        <v>372.4</v>
+      </c>
+      <c r="D496" t="n">
+        <v>366.76</v>
+      </c>
+      <c r="E496" t="n">
+        <v>360.84</v>
+      </c>
+      <c r="F496" t="n">
+        <v>347.63</v>
+      </c>
+      <c r="G496" t="n">
+        <v>338.13</v>
+      </c>
+      <c r="H496" t="n">
+        <v>334.47</v>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>373.37</v>
+      </c>
+      <c r="C497" t="n">
+        <v>373.44</v>
+      </c>
+      <c r="D497" t="n">
+        <v>368.35</v>
+      </c>
+      <c r="E497" t="n">
+        <v>362.36</v>
+      </c>
+      <c r="F497" t="n">
+        <v>350.48</v>
+      </c>
+      <c r="G497" t="n">
+        <v>341.67</v>
+      </c>
+      <c r="H497" t="n">
+        <v>338.32</v>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>372.43</v>
+      </c>
+      <c r="C498" t="n">
+        <v>372.83</v>
+      </c>
+      <c r="D498" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="E498" t="n">
+        <v>362.99</v>
+      </c>
+      <c r="F498" t="n">
+        <v>350.79</v>
+      </c>
+      <c r="G498" t="n">
+        <v>341.88</v>
+      </c>
+      <c r="H498" t="n">
+        <v>339.02</v>
+      </c>
+      <c r="I498" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16785,7 +16884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21958,6 +22057,36 @@
       </c>
       <c r="B517" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>
@@ -22126,28 +22255,28 @@
         <v>0.188</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06402882737831996</v>
+        <v>-0.06528039635541666</v>
       </c>
       <c r="J2" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K2" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00351042045489558</v>
+        <v>0.003689750626163613</v>
       </c>
       <c r="M2" t="n">
-        <v>6.993994344069572</v>
+        <v>6.958180683554858</v>
       </c>
       <c r="N2" t="n">
-        <v>73.46003681087009</v>
+        <v>73.02872152548373</v>
       </c>
       <c r="O2" t="n">
-        <v>8.570883082324137</v>
+        <v>8.54568438017013</v>
       </c>
       <c r="P2" t="n">
-        <v>375.3424260192655</v>
+        <v>375.3546301944573</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22204,28 +22333,28 @@
         <v>0.1905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.108683450917608</v>
+        <v>0.1062948385796976</v>
       </c>
       <c r="J3" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K3" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007688975824047262</v>
+        <v>0.007438773109779029</v>
       </c>
       <c r="M3" t="n">
-        <v>7.503947942278302</v>
+        <v>7.46944829018104</v>
       </c>
       <c r="N3" t="n">
-        <v>96.22603261830092</v>
+        <v>95.67773742593384</v>
       </c>
       <c r="O3" t="n">
-        <v>9.80948686824652</v>
+        <v>9.781499753408669</v>
       </c>
       <c r="P3" t="n">
-        <v>372.3108017950147</v>
+        <v>372.334098784653</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22282,28 +22411,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0937544571427934</v>
+        <v>0.08598497602509918</v>
       </c>
       <c r="J4" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K4" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007539716178711187</v>
+        <v>0.006392743182292104</v>
       </c>
       <c r="M4" t="n">
-        <v>6.636674191171728</v>
+        <v>6.632995417219465</v>
       </c>
       <c r="N4" t="n">
-        <v>73.03455803620355</v>
+        <v>72.92949319790526</v>
       </c>
       <c r="O4" t="n">
-        <v>8.546025862130511</v>
+        <v>8.539876650040402</v>
       </c>
       <c r="P4" t="n">
-        <v>372.7760839046283</v>
+        <v>372.8518622209095</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22360,28 +22489,28 @@
         <v>0.1532</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09001812048112795</v>
+        <v>0.08292094113480968</v>
       </c>
       <c r="J5" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K5" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005803780959252713</v>
+        <v>0.004969400442429439</v>
       </c>
       <c r="M5" t="n">
-        <v>7.186371400777753</v>
+        <v>7.171298044706263</v>
       </c>
       <c r="N5" t="n">
-        <v>87.72693186275116</v>
+        <v>87.47952737114873</v>
       </c>
       <c r="O5" t="n">
-        <v>9.366265630588915</v>
+        <v>9.353049094875358</v>
       </c>
       <c r="P5" t="n">
-        <v>366.5227680225944</v>
+        <v>366.5919707576566</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22438,28 +22567,28 @@
         <v>0.1625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06510961461743044</v>
+        <v>0.05535508979866855</v>
       </c>
       <c r="J6" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K6" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002861023980838984</v>
+        <v>0.002081346415792829</v>
       </c>
       <c r="M6" t="n">
-        <v>8.04121544824145</v>
+        <v>8.037273647049105</v>
       </c>
       <c r="N6" t="n">
-        <v>93.36747260441734</v>
+        <v>93.34059692352193</v>
       </c>
       <c r="O6" t="n">
-        <v>9.66268454439124</v>
+        <v>9.661293749986175</v>
       </c>
       <c r="P6" t="n">
-        <v>357.315453400665</v>
+        <v>357.4105743335218</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22516,28 +22645,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006735430391957924</v>
+        <v>-0.002467804193273771</v>
       </c>
       <c r="J7" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K7" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L7" t="n">
-        <v>3.645273140640004e-05</v>
+        <v>4.919393992608434e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>6.979168025175383</v>
+        <v>6.98346799073142</v>
       </c>
       <c r="N7" t="n">
-        <v>78.64225472822127</v>
+        <v>78.65246463417894</v>
       </c>
       <c r="O7" t="n">
-        <v>8.868046838409306</v>
+        <v>8.86862247669721</v>
       </c>
       <c r="P7" t="n">
-        <v>349.2507268221391</v>
+        <v>349.3404687352524</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22594,28 +22723,28 @@
         <v>0.1377</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05466097896412758</v>
+        <v>-0.06218471759093706</v>
       </c>
       <c r="J8" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K8" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003314451496820192</v>
+        <v>0.004309042183649026</v>
       </c>
       <c r="M8" t="n">
-        <v>5.906499737262004</v>
+        <v>5.913839621393932</v>
       </c>
       <c r="N8" t="n">
-        <v>56.71366641162147</v>
+        <v>56.70765646940152</v>
       </c>
       <c r="O8" t="n">
-        <v>7.530847655584427</v>
+        <v>7.530448623382376</v>
       </c>
       <c r="P8" t="n">
-        <v>345.9751574054189</v>
+        <v>346.0485261437929</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22653,7 +22782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I495"/>
+  <dimension ref="A1:I498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45909,6 +46038,147 @@
         </is>
       </c>
     </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>-41.0774175854599,172.1031277954876</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-41.07674660225383,172.10300564745108</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-41.07606871353554,172.10296057155156</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-41.075390521722554,172.10291880409457</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>-41.074704609657694,172.10296320739732</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-41.074022616212886,172.10296375350902</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-41.073346795177414,172.1028952664387</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-41.07741954291239,172.10310592647528</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-41.076747702652156,172.10299335364397</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-41.07607039587531,172.10294177640503</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-41.07539212999813,172.10290083659226</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-41.074707625199316,172.10292951868402</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>-41.07402636184933,172.10292190901575</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>-41.07335086881286,172.1028497580622</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-41.07741854831543,172.10311703829788</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-41.07674705722638,172.1030005644347</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-41.07607023716414,172.1029435495321</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-41.07539279658521,172.10289338953515</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-41.07470795320501,172.1029258542975</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-41.07402658404761,172.10291942671515</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-41.07335160947191,172.10284148381137</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0339/nzd0339.xlsx
+++ b/data/nzd0339/nzd0339.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I498"/>
+  <dimension ref="A1:I500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16868,6 +16868,72 @@
         <v>339.02</v>
       </c>
       <c r="I498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>374.93</v>
+      </c>
+      <c r="C499" t="n">
+        <v>376.03</v>
+      </c>
+      <c r="D499" t="n">
+        <v>369.95</v>
+      </c>
+      <c r="E499" t="n">
+        <v>363.68</v>
+      </c>
+      <c r="F499" t="n">
+        <v>351.92</v>
+      </c>
+      <c r="G499" t="n">
+        <v>342.77</v>
+      </c>
+      <c r="H499" t="n">
+        <v>339.15</v>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>374.15</v>
+      </c>
+      <c r="C500" t="n">
+        <v>375.86</v>
+      </c>
+      <c r="D500" t="n">
+        <v>370.75</v>
+      </c>
+      <c r="E500" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="F500" t="n">
+        <v>353.34</v>
+      </c>
+      <c r="G500" t="n">
+        <v>344.75</v>
+      </c>
+      <c r="H500" t="n">
+        <v>340.95</v>
+      </c>
+      <c r="I500" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16884,7 +16950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B520"/>
+  <dimension ref="A1:B522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22087,6 +22153,26 @@
       </c>
       <c r="B520" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>-0.04</v>
       </c>
     </row>
   </sheetData>
@@ -22255,28 +22341,28 @@
         <v>0.188</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06528039635541666</v>
+        <v>-0.06465080355293074</v>
       </c>
       <c r="J2" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K2" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003689750626163613</v>
+        <v>0.003646416334857183</v>
       </c>
       <c r="M2" t="n">
-        <v>6.958180683554858</v>
+        <v>6.934361306310699</v>
       </c>
       <c r="N2" t="n">
-        <v>73.02872152548373</v>
+        <v>72.73995178339914</v>
       </c>
       <c r="O2" t="n">
-        <v>8.54568438017013</v>
+        <v>8.528771997386208</v>
       </c>
       <c r="P2" t="n">
-        <v>375.3546301944573</v>
+        <v>375.3484700303528</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22333,28 +22419,28 @@
         <v>0.1905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1062948385796976</v>
+        <v>0.106838410031156</v>
       </c>
       <c r="J3" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K3" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007438773109779029</v>
+        <v>0.00757101388947945</v>
       </c>
       <c r="M3" t="n">
-        <v>7.46944829018104</v>
+        <v>7.443346227978687</v>
       </c>
       <c r="N3" t="n">
-        <v>95.67773742593384</v>
+        <v>95.29676334897167</v>
       </c>
       <c r="O3" t="n">
-        <v>9.781499753408669</v>
+        <v>9.762006112934557</v>
       </c>
       <c r="P3" t="n">
-        <v>372.334098784653</v>
+        <v>372.3287781467207</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22411,28 +22497,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08598497602509918</v>
+        <v>0.0826958319659907</v>
       </c>
       <c r="J4" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K4" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006392743182292104</v>
+        <v>0.005953163633243053</v>
       </c>
       <c r="M4" t="n">
-        <v>6.632995417219465</v>
+        <v>6.621923905558392</v>
       </c>
       <c r="N4" t="n">
-        <v>72.92949319790526</v>
+        <v>72.72842618231429</v>
       </c>
       <c r="O4" t="n">
-        <v>8.539876650040402</v>
+        <v>8.528096281252592</v>
       </c>
       <c r="P4" t="n">
-        <v>372.8518622209095</v>
+        <v>372.8840583402284</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22489,28 +22575,28 @@
         <v>0.1532</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08292094113480968</v>
+        <v>0.07956710828848403</v>
       </c>
       <c r="J5" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K5" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004969400442429439</v>
+        <v>0.00460699314383739</v>
       </c>
       <c r="M5" t="n">
-        <v>7.171298044706263</v>
+        <v>7.155879070491222</v>
       </c>
       <c r="N5" t="n">
-        <v>87.47952737114873</v>
+        <v>87.22281716414888</v>
       </c>
       <c r="O5" t="n">
-        <v>9.353049094875358</v>
+        <v>9.339315668942177</v>
       </c>
       <c r="P5" t="n">
-        <v>366.5919707576566</v>
+        <v>366.6247948467155</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22567,28 +22653,28 @@
         <v>0.1625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05535508979866855</v>
+        <v>0.05105559531970368</v>
       </c>
       <c r="J6" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K6" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002081346415792829</v>
+        <v>0.00178156142812036</v>
       </c>
       <c r="M6" t="n">
-        <v>8.037273647049105</v>
+        <v>8.024909808699364</v>
       </c>
       <c r="N6" t="n">
-        <v>93.34059692352193</v>
+        <v>93.12290754926265</v>
       </c>
       <c r="O6" t="n">
-        <v>9.661293749986175</v>
+        <v>9.650021116519001</v>
       </c>
       <c r="P6" t="n">
-        <v>357.4105743335218</v>
+        <v>357.4526536410347</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22645,28 +22731,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.002467804193273771</v>
+        <v>-0.006259964891135659</v>
       </c>
       <c r="J7" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K7" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L7" t="n">
-        <v>4.919393992608434e-06</v>
+        <v>3.184341539708146e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>6.98346799073142</v>
+        <v>6.974695012882366</v>
       </c>
       <c r="N7" t="n">
-        <v>78.65246463417894</v>
+        <v>78.46127752234443</v>
       </c>
       <c r="O7" t="n">
-        <v>8.86862247669721</v>
+        <v>8.85783706794974</v>
       </c>
       <c r="P7" t="n">
-        <v>349.3404687352524</v>
+        <v>349.3775796033892</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22723,28 +22809,28 @@
         <v>0.1377</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06218471759093706</v>
+        <v>-0.06517524177806719</v>
       </c>
       <c r="J8" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K8" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004309042183649026</v>
+        <v>0.004760716415042388</v>
       </c>
       <c r="M8" t="n">
-        <v>5.913839621393932</v>
+        <v>5.907196656980892</v>
       </c>
       <c r="N8" t="n">
-        <v>56.70765646940152</v>
+        <v>56.55856996519847</v>
       </c>
       <c r="O8" t="n">
-        <v>7.530448623382376</v>
+        <v>7.520543196152686</v>
       </c>
       <c r="P8" t="n">
-        <v>346.0485261437929</v>
+        <v>346.0777945791033</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22782,7 +22868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I498"/>
+  <dimension ref="A1:I500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46179,6 +46265,100 @@
         </is>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-41.07742119351775,172.10308748557745</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-41.07675044306152,172.10296273733425</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-41.07607208879271,172.10292286304912</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-41.07539352665623,172.10288523323433</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-41.074709148837634,172.10291249701726</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-41.07402752574455,172.10290890648864</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-41.07335174702281,172.10283994716477</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-41.07742036821544,172.10309670602646</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-41.07675026318935,172.10296474689906</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-41.07607293525026,172.10291340637082</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-41.07539402395064,172.10287967749312</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-41.074710651311854,172.10289571176182</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-41.07402962075224,172.10288550193883</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-41.07335365157164,172.10281867051884</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0339/nzd0339.xlsx
+++ b/data/nzd0339/nzd0339.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I500"/>
+  <dimension ref="A1:I504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16934,6 +16934,138 @@
         <v>340.95</v>
       </c>
       <c r="I500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>372.86</v>
+      </c>
+      <c r="C501" t="n">
+        <v>374.8</v>
+      </c>
+      <c r="D501" t="n">
+        <v>370.32</v>
+      </c>
+      <c r="E501" t="n">
+        <v>364.95</v>
+      </c>
+      <c r="F501" t="n">
+        <v>354.71</v>
+      </c>
+      <c r="G501" t="n">
+        <v>345.84</v>
+      </c>
+      <c r="H501" t="n">
+        <v>342.41</v>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:19:02+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>373.66</v>
+      </c>
+      <c r="C502" t="n">
+        <v>376.23</v>
+      </c>
+      <c r="D502" t="n">
+        <v>372.83</v>
+      </c>
+      <c r="E502" t="n">
+        <v>367.85</v>
+      </c>
+      <c r="F502" t="n">
+        <v>358.87</v>
+      </c>
+      <c r="G502" t="n">
+        <v>351.93</v>
+      </c>
+      <c r="H502" t="n">
+        <v>347.05</v>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>372.58</v>
+      </c>
+      <c r="C503" t="n">
+        <v>375.91</v>
+      </c>
+      <c r="D503" t="n">
+        <v>372.24</v>
+      </c>
+      <c r="E503" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="F503" t="n">
+        <v>358.76</v>
+      </c>
+      <c r="G503" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="H503" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>373.69</v>
+      </c>
+      <c r="C504" t="n">
+        <v>377.61</v>
+      </c>
+      <c r="D504" t="n">
+        <v>373.35</v>
+      </c>
+      <c r="E504" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="F504" t="n">
+        <v>360.31</v>
+      </c>
+      <c r="G504" t="n">
+        <v>352.99</v>
+      </c>
+      <c r="H504" t="n">
+        <v>347.88</v>
+      </c>
+      <c r="I504" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16950,7 +17082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B522"/>
+  <dimension ref="A1:B526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22173,6 +22305,46 @@
       </c>
       <c r="B522" t="n">
         <v>-0.04</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -22341,28 +22513,28 @@
         <v>0.188</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06465080355293074</v>
+        <v>-0.06523265126526777</v>
       </c>
       <c r="J2" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K2" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003646416334857183</v>
+        <v>0.003768049760484615</v>
       </c>
       <c r="M2" t="n">
-        <v>6.934361306310699</v>
+        <v>6.882666917135081</v>
       </c>
       <c r="N2" t="n">
-        <v>72.73995178339914</v>
+        <v>72.16484189300068</v>
       </c>
       <c r="O2" t="n">
-        <v>8.528771997386208</v>
+        <v>8.494989222653592</v>
       </c>
       <c r="P2" t="n">
-        <v>375.3484700303528</v>
+        <v>375.3541909554453</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22419,28 +22591,28 @@
         <v>0.1905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.106838410031156</v>
+        <v>0.1081455923288735</v>
       </c>
       <c r="J3" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K3" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00757101388947945</v>
+        <v>0.007871494167067894</v>
       </c>
       <c r="M3" t="n">
-        <v>7.443346227978687</v>
+        <v>7.394782651405979</v>
       </c>
       <c r="N3" t="n">
-        <v>95.29676334897167</v>
+        <v>94.55405646802471</v>
       </c>
       <c r="O3" t="n">
-        <v>9.762006112934557</v>
+        <v>9.723891014816276</v>
       </c>
       <c r="P3" t="n">
-        <v>372.3287781467207</v>
+        <v>372.3158964117447</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22497,28 +22669,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0826958319659907</v>
+        <v>0.07876533187599073</v>
       </c>
       <c r="J4" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K4" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005953163633243053</v>
+        <v>0.005479520469786836</v>
       </c>
       <c r="M4" t="n">
-        <v>6.621923905558392</v>
+        <v>6.587678129961722</v>
       </c>
       <c r="N4" t="n">
-        <v>72.72842618231429</v>
+        <v>72.22593279516147</v>
       </c>
       <c r="O4" t="n">
-        <v>8.528096281252592</v>
+        <v>8.498584164151195</v>
       </c>
       <c r="P4" t="n">
-        <v>372.8840583402284</v>
+        <v>372.9227064562589</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22575,28 +22747,28 @@
         <v>0.1532</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07956710828848403</v>
+        <v>0.07756416199595201</v>
       </c>
       <c r="J5" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K5" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00460699314383739</v>
+        <v>0.004443395754759938</v>
       </c>
       <c r="M5" t="n">
-        <v>7.155879070491222</v>
+        <v>7.106961443323117</v>
       </c>
       <c r="N5" t="n">
-        <v>87.22281716414888</v>
+        <v>86.56038318713132</v>
       </c>
       <c r="O5" t="n">
-        <v>9.339315668942177</v>
+        <v>9.303783272794531</v>
       </c>
       <c r="P5" t="n">
-        <v>366.6247948467155</v>
+        <v>366.6444678454694</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22653,28 +22825,28 @@
         <v>0.1625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05105559531970368</v>
+        <v>0.05017806718139314</v>
       </c>
       <c r="J6" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K6" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00178156142812036</v>
+        <v>0.001746278541733925</v>
       </c>
       <c r="M6" t="n">
-        <v>8.024909808699364</v>
+        <v>7.971320310185559</v>
       </c>
       <c r="N6" t="n">
-        <v>93.12290754926265</v>
+        <v>92.41880138369277</v>
       </c>
       <c r="O6" t="n">
-        <v>9.650021116519001</v>
+        <v>9.613469788983204</v>
       </c>
       <c r="P6" t="n">
-        <v>357.4526536410347</v>
+        <v>357.4612409341824</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22731,28 +22903,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.006259964891135659</v>
+        <v>-0.004416512273187043</v>
       </c>
       <c r="J7" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K7" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L7" t="n">
-        <v>3.184341539708146e-05</v>
+        <v>1.607507191814239e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>6.974695012882366</v>
+        <v>6.944519930486009</v>
       </c>
       <c r="N7" t="n">
-        <v>78.46127752234443</v>
+        <v>77.91194231368705</v>
       </c>
       <c r="O7" t="n">
-        <v>8.85783706794974</v>
+        <v>8.826774173710747</v>
       </c>
       <c r="P7" t="n">
-        <v>349.3775796033892</v>
+        <v>349.3593851947473</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22809,28 +22981,28 @@
         <v>0.1377</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06517524177806719</v>
+        <v>-0.06293809664993209</v>
       </c>
       <c r="J8" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K8" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004760716415042388</v>
+        <v>0.004503495931016066</v>
       </c>
       <c r="M8" t="n">
-        <v>5.907196656980892</v>
+        <v>5.88110504803127</v>
       </c>
       <c r="N8" t="n">
-        <v>56.55856996519847</v>
+        <v>56.16541115983554</v>
       </c>
       <c r="O8" t="n">
-        <v>7.520543196152686</v>
+        <v>7.494358622312888</v>
       </c>
       <c r="P8" t="n">
-        <v>346.0777945791033</v>
+        <v>346.0557391465309</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22868,7 +23040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I500"/>
+  <dimension ref="A1:I504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46359,6 +46531,194 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-41.077419003290764,172.10311195523013</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-41.07674914163262,172.10297727712643</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-41.07607248027942,172.10291848933542</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-41.075394870408616,172.10287022091214</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-41.074712100879715,172.1028795175358</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-41.07403077406252,172.10287261761533</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-41.073355196369455,172.10280141279407</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:19:02+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-41.07741984975593,172.10310249835973</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-41.07675065467581,172.10296037314038</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-41.076075136036216,172.10288881900615</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-41.07539793881219,172.1028359408041</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-41.074716502473244,172.10283034382348</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-41.074037217760335,172.1028006308827</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-41.073360105846675,172.1027465663213</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-41.07741870702778,172.10311526513473</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-41.076750316092934,172.1029641558506</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-41.076074511775346,172.10289579330689</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-41.0753976319723,172.102839368815</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-41.07471638608522,172.10283164408997</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-41.07403676278807,172.1028057136902</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-41.07335962971317,172.10275188548388</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-41.077419881498344,172.10310214372706</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-41.07675211481304,172.10294406020208</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-41.07607568623188,172.10288267216475</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-41.07539882758926,172.10282601139292</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-41.07471802609687,172.1028133221524</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-41.07403833931889,172.10278810117094</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-41.07336098404779,172.10273675542126</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0339/nzd0339.xlsx
+++ b/data/nzd0339/nzd0339.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I504"/>
+  <dimension ref="A1:I507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17066,6 +17066,105 @@
         <v>347.88</v>
       </c>
       <c r="I504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:18:41+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>370.74</v>
+      </c>
+      <c r="C505" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="D505" t="n">
+        <v>371.93</v>
+      </c>
+      <c r="E505" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="F505" t="n">
+        <v>360.29</v>
+      </c>
+      <c r="G505" t="n">
+        <v>353.34</v>
+      </c>
+      <c r="H505" t="n">
+        <v>349.44</v>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>369.84</v>
+      </c>
+      <c r="C506" t="n">
+        <v>374.88</v>
+      </c>
+      <c r="D506" t="n">
+        <v>371.17</v>
+      </c>
+      <c r="E506" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="F506" t="n">
+        <v>360.22</v>
+      </c>
+      <c r="G506" t="n">
+        <v>353.35</v>
+      </c>
+      <c r="H506" t="n">
+        <v>349.59</v>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>368.04</v>
+      </c>
+      <c r="C507" t="n">
+        <v>373.68</v>
+      </c>
+      <c r="D507" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="E507" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="F507" t="n">
+        <v>360.01</v>
+      </c>
+      <c r="G507" t="n">
+        <v>353.44</v>
+      </c>
+      <c r="H507" t="n">
+        <v>349.43</v>
+      </c>
+      <c r="I507" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17082,7 +17181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B526"/>
+  <dimension ref="A1:B529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22345,6 +22444,36 @@
       </c>
       <c r="B526" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>
@@ -22513,28 +22642,28 @@
         <v>0.188</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06523265126526777</v>
+        <v>-0.06933481199848794</v>
       </c>
       <c r="J2" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K2" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003768049760484615</v>
+        <v>0.004296058211061604</v>
       </c>
       <c r="M2" t="n">
-        <v>6.882666917135081</v>
+        <v>6.863048377149564</v>
       </c>
       <c r="N2" t="n">
-        <v>72.16484189300068</v>
+        <v>71.84111556644868</v>
       </c>
       <c r="O2" t="n">
-        <v>8.494989222653592</v>
+        <v>8.475913848456027</v>
       </c>
       <c r="P2" t="n">
-        <v>375.3541909554453</v>
+        <v>375.3947283028829</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22591,28 +22720,28 @@
         <v>0.1905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1081455923288735</v>
+        <v>0.1077112481527179</v>
       </c>
       <c r="J3" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K3" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007871494167067894</v>
+        <v>0.007895272884004489</v>
       </c>
       <c r="M3" t="n">
-        <v>7.394782651405979</v>
+        <v>7.35520167985795</v>
       </c>
       <c r="N3" t="n">
-        <v>94.55405646802471</v>
+        <v>93.99890721428119</v>
       </c>
       <c r="O3" t="n">
-        <v>9.723891014816276</v>
+        <v>9.695303358548466</v>
       </c>
       <c r="P3" t="n">
-        <v>372.3158964117447</v>
+        <v>372.3201964644416</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22669,28 +22798,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07876533187599073</v>
+        <v>0.07491811180760875</v>
       </c>
       <c r="J4" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K4" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005479520469786836</v>
+        <v>0.005009172726981315</v>
       </c>
       <c r="M4" t="n">
-        <v>6.587678129961722</v>
+        <v>6.566520408775558</v>
       </c>
       <c r="N4" t="n">
-        <v>72.22593279516147</v>
+        <v>71.88479356021297</v>
       </c>
       <c r="O4" t="n">
-        <v>8.498584164151195</v>
+        <v>8.478490051902696</v>
       </c>
       <c r="P4" t="n">
-        <v>372.9227064562589</v>
+        <v>372.9607186477435</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22747,28 +22876,28 @@
         <v>0.1532</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07756416199595201</v>
+        <v>0.07678702063079872</v>
       </c>
       <c r="J5" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K5" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004443395754759938</v>
+        <v>0.004403512891703709</v>
       </c>
       <c r="M5" t="n">
-        <v>7.106961443323117</v>
+        <v>7.067864747732147</v>
       </c>
       <c r="N5" t="n">
-        <v>86.56038318713132</v>
+        <v>86.05063032119361</v>
       </c>
       <c r="O5" t="n">
-        <v>9.303783272794531</v>
+        <v>9.276347897809439</v>
       </c>
       <c r="P5" t="n">
-        <v>366.6444678454694</v>
+        <v>366.6521479095847</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22825,28 +22954,28 @@
         <v>0.1625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05017806718139314</v>
+        <v>0.05156018596603139</v>
       </c>
       <c r="J6" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K6" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001746278541733925</v>
+        <v>0.001864004264720776</v>
       </c>
       <c r="M6" t="n">
-        <v>7.971320310185559</v>
+        <v>7.933583534310162</v>
       </c>
       <c r="N6" t="n">
-        <v>92.41880138369277</v>
+        <v>91.88087488709483</v>
       </c>
       <c r="O6" t="n">
-        <v>9.613469788983204</v>
+        <v>9.585451209363846</v>
       </c>
       <c r="P6" t="n">
-        <v>357.4612409341824</v>
+        <v>357.4475896931467</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22903,28 +23032,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.004416512273187043</v>
+        <v>-0.0002520556373612125</v>
       </c>
       <c r="J7" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K7" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L7" t="n">
-        <v>1.607507191814239e-05</v>
+        <v>5.287733384484739e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.944519930486009</v>
+        <v>6.930529974058591</v>
       </c>
       <c r="N7" t="n">
-        <v>77.91194231368705</v>
+        <v>77.54907364379507</v>
       </c>
       <c r="O7" t="n">
-        <v>8.826774173710747</v>
+        <v>8.806195185424581</v>
       </c>
       <c r="P7" t="n">
-        <v>349.3593851947473</v>
+        <v>349.3182481249632</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22981,28 +23110,28 @@
         <v>0.1377</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06293809664993209</v>
+        <v>-0.05778987786208295</v>
       </c>
       <c r="J8" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K8" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004503495931016066</v>
+        <v>0.003831560432483783</v>
       </c>
       <c r="M8" t="n">
-        <v>5.88110504803127</v>
+        <v>5.876458889403086</v>
       </c>
       <c r="N8" t="n">
-        <v>56.16541115983554</v>
+        <v>55.98490759031962</v>
       </c>
       <c r="O8" t="n">
-        <v>7.494358622312888</v>
+        <v>7.482306301557002</v>
       </c>
       <c r="P8" t="n">
-        <v>346.0557391465309</v>
+        <v>346.0048807011792</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23040,7 +23169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I504"/>
+  <dimension ref="A1:I507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46719,6 +46848,147 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:18:41+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-41.07741676015436,172.10313701593566</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-41.076750167962885,172.10296581078632</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-41.0760741837737,172.1028994577699</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-41.075398584233724,172.1028287301603</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-41.07471800493545,172.1028135585645</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-41.07403870964452,172.10278396400187</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-41.07336263464043,172.10271831565666</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-41.07741580787781,172.10314765491393</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-41.076749226278444,172.1029763314489</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-41.07607337964016,172.10290844161463</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-41.0753980022963,172.10283523156042</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-41.07471793087046,172.10281438600686</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-41.07403872022525,172.102783845797</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-41.073362793351116,172.10271654260234</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-41.07741390332175,172.1031689328696</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-41.07674795659004,172.10299051661153</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-41.0760726918938,172.10291612516585</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-41.07539752616542,172.10284055088775</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>-41.074717708675486,172.10281686833395</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>-41.07403881545182,172.10278278195352</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>-41.07336262405973,172.1027184338603</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0339/nzd0339.xlsx
+++ b/data/nzd0339/nzd0339.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I507"/>
+  <dimension ref="A1:I511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17165,6 +17165,138 @@
         <v>349.43</v>
       </c>
       <c r="I507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>368.73</v>
+      </c>
+      <c r="C508" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="D508" t="n">
+        <v>371.08</v>
+      </c>
+      <c r="E508" t="n">
+        <v>368.15</v>
+      </c>
+      <c r="F508" t="n">
+        <v>360.79</v>
+      </c>
+      <c r="G508" t="n">
+        <v>354.06</v>
+      </c>
+      <c r="H508" t="n">
+        <v>350.12</v>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>369.17</v>
+      </c>
+      <c r="C509" t="n">
+        <v>373.73</v>
+      </c>
+      <c r="D509" t="n">
+        <v>371.85</v>
+      </c>
+      <c r="E509" t="n">
+        <v>368.92</v>
+      </c>
+      <c r="F509" t="n">
+        <v>361.86</v>
+      </c>
+      <c r="G509" t="n">
+        <v>354.5</v>
+      </c>
+      <c r="H509" t="n">
+        <v>350.03</v>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>369.67</v>
+      </c>
+      <c r="C510" t="n">
+        <v>373.85</v>
+      </c>
+      <c r="D510" t="n">
+        <v>372.03</v>
+      </c>
+      <c r="E510" t="n">
+        <v>369.35</v>
+      </c>
+      <c r="F510" t="n">
+        <v>361.64</v>
+      </c>
+      <c r="G510" t="n">
+        <v>354.03</v>
+      </c>
+      <c r="H510" t="n">
+        <v>348.72</v>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>369.78</v>
+      </c>
+      <c r="C511" t="n">
+        <v>373.49</v>
+      </c>
+      <c r="D511" t="n">
+        <v>371.99</v>
+      </c>
+      <c r="E511" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="F511" t="n">
+        <v>361.56</v>
+      </c>
+      <c r="G511" t="n">
+        <v>353.99</v>
+      </c>
+      <c r="H511" t="n">
+        <v>349.09</v>
+      </c>
+      <c r="I511" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17181,7 +17313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22474,6 +22606,56 @@
       </c>
       <c r="B529" t="n">
         <v>1.75</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -22642,28 +22824,28 @@
         <v>0.188</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06933481199848794</v>
+        <v>-0.07488821767706945</v>
       </c>
       <c r="J2" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K2" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004296058211061604</v>
+        <v>0.005072383844320849</v>
       </c>
       <c r="M2" t="n">
-        <v>6.863048377149564</v>
+        <v>6.837513878170018</v>
       </c>
       <c r="N2" t="n">
-        <v>71.84111556644868</v>
+        <v>71.41423280723625</v>
       </c>
       <c r="O2" t="n">
-        <v>8.475913848456027</v>
+        <v>8.450694220431611</v>
       </c>
       <c r="P2" t="n">
-        <v>375.3947283028829</v>
+        <v>375.4498490576596</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22720,28 +22902,28 @@
         <v>0.1905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1077112481527179</v>
+        <v>0.1057595795501151</v>
       </c>
       <c r="J3" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K3" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007895272884004489</v>
+        <v>0.00772446556784967</v>
       </c>
       <c r="M3" t="n">
-        <v>7.35520167985795</v>
+        <v>7.306524339285309</v>
       </c>
       <c r="N3" t="n">
-        <v>93.99890721428119</v>
+        <v>93.278527954914</v>
       </c>
       <c r="O3" t="n">
-        <v>9.695303358548466</v>
+        <v>9.658080966471237</v>
       </c>
       <c r="P3" t="n">
-        <v>372.3201964644416</v>
+        <v>372.3395722343436</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22798,28 +22980,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07491811180760875</v>
+        <v>0.07064645291786303</v>
       </c>
       <c r="J4" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K4" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005009172726981315</v>
+        <v>0.004517327670211069</v>
       </c>
       <c r="M4" t="n">
-        <v>6.566520408775558</v>
+        <v>6.534715085450364</v>
       </c>
       <c r="N4" t="n">
-        <v>71.88479356021297</v>
+        <v>71.40214265782841</v>
       </c>
       <c r="O4" t="n">
-        <v>8.478490051902696</v>
+        <v>8.44997885546635</v>
       </c>
       <c r="P4" t="n">
-        <v>372.9607186477435</v>
+        <v>373.003116351528</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22876,28 +23058,28 @@
         <v>0.1532</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07678702063079872</v>
+        <v>0.07712655615005909</v>
       </c>
       <c r="J5" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K5" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004403512891703709</v>
+        <v>0.004507691328741958</v>
       </c>
       <c r="M5" t="n">
-        <v>7.067864747732147</v>
+        <v>7.017135659773383</v>
       </c>
       <c r="N5" t="n">
-        <v>86.05063032119361</v>
+        <v>85.37694703672385</v>
       </c>
       <c r="O5" t="n">
-        <v>9.276347897809439</v>
+        <v>9.239964666421828</v>
       </c>
       <c r="P5" t="n">
-        <v>366.6521479095847</v>
+        <v>366.6487696294427</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22954,28 +23136,28 @@
         <v>0.1625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05156018596603139</v>
+        <v>0.05504464427673501</v>
       </c>
       <c r="J6" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K6" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001864004264720776</v>
+        <v>0.002153987289316373</v>
       </c>
       <c r="M6" t="n">
-        <v>7.933583534310162</v>
+        <v>7.895315435067672</v>
       </c>
       <c r="N6" t="n">
-        <v>91.88087488709483</v>
+        <v>91.21337059570966</v>
       </c>
       <c r="O6" t="n">
-        <v>9.585451209363846</v>
+        <v>9.550569124178395</v>
       </c>
       <c r="P6" t="n">
-        <v>357.4475896931467</v>
+        <v>357.4129975108249</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23032,28 +23214,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0002520556373612125</v>
+        <v>0.00613928564954999</v>
       </c>
       <c r="J7" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K7" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="L7" t="n">
-        <v>5.287733384484739e-08</v>
+        <v>3.175898563989588e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>6.930529974058591</v>
+        <v>6.917420764424016</v>
       </c>
       <c r="N7" t="n">
-        <v>77.54907364379507</v>
+        <v>77.11932880556506</v>
       </c>
       <c r="O7" t="n">
-        <v>8.806195185424581</v>
+        <v>8.781761144870945</v>
       </c>
       <c r="P7" t="n">
-        <v>349.3182481249632</v>
+        <v>349.2548077388122</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23110,28 +23292,28 @@
         <v>0.1377</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05778987786208295</v>
+        <v>-0.05112970512427594</v>
       </c>
       <c r="J8" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K8" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003831560432483783</v>
+        <v>0.00303538731799835</v>
       </c>
       <c r="M8" t="n">
-        <v>5.876458889403086</v>
+        <v>5.869268582421035</v>
       </c>
       <c r="N8" t="n">
-        <v>55.98490759031962</v>
+        <v>55.74303552613092</v>
       </c>
       <c r="O8" t="n">
-        <v>7.482306301557002</v>
+        <v>7.466125871302394</v>
       </c>
       <c r="P8" t="n">
-        <v>346.0048807011792</v>
+        <v>345.9387734014493</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23169,7 +23351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I507"/>
+  <dimension ref="A1:I511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46989,6 +47171,194 @@
         </is>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-41.07741463340203,172.10316077632004</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-41.07674814704342,172.10298838883716</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-41.076073284413766,172.10290950549097</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-41.075398256232674,172.10283239458582</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>-41.07471853397086,172.10280764826186</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>-41.07403947145679,172.1027754532539</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>-41.0733633541286,172.1027102778103</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-41.07741509896018,172.10315557504202</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-41.07674800949377,172.1029899255631</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-41.07607409912811,172.1029004034378</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-41.07539907094473,172.10282329262554</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>-41.07471966610557,172.10279500021392</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>-41.07403993700843,172.10277025224119</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-41.07336325890227,172.1027113416429</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-41.07741562800324,172.1031496644987</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-41.07674813646268,172.10298850704683</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-41.076074289580696,172.10289827568505</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-41.075399525913475,172.10281820971255</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-41.07471943333033,172.10279760074718</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-41.074039439714625,172.1027758078684</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-41.07336187282881,172.10272682631734</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-41.07741574439266,172.10314836417913</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-41.07674775555589,172.10299276259553</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-41.0760742472579,172.102898748519</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-41.07539963172014,172.10281702763976</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-41.074719348684766,172.10279854639563</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-41.074039397391736,172.10277628068772</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-41.07336226431542,172.1027224527834</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
